--- a/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152302.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152302.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9090AB08-61D7-41AA-B752-A4D9F7E1D448}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92668137-FC1F-44DF-8380-6C68F443037D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AA6EEDD-033B-4056-B94B-66253479E5C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34875697-588C-4C44-8905-6736A76EA9E8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9F4B519-8AA6-40C0-A06D-576011C59FE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40D547D0-01E6-442D-B879-1BE897A9E44B}"/>
 </file>
--- a/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152302.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152302.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92668137-FC1F-44DF-8380-6C68F443037D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9090AB08-61D7-41AA-B752-A4D9F7E1D448}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34875697-588C-4C44-8905-6736A76EA9E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AA6EEDD-033B-4056-B94B-66253479E5C1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40D547D0-01E6-442D-B879-1BE897A9E44B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9F4B519-8AA6-40C0-A06D-576011C59FE9}"/>
 </file>